--- a/output_data/charts/0500000US39049.xlsx
+++ b/output_data/charts/0500000US39049.xlsx
@@ -167,10 +167,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -212,16 +212,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$15</c:f>
+              <c:f>Sheet1!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>3.91882135244011</c:v>
                 </c:pt>
@@ -253,16 +256,19 @@
                   <c:v>5.800953315447926</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.798219777249421</c:v>
+                  <c:v>5.799449605701753</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.853056068792861</c:v>
+                  <c:v>5.853517877739331</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.864737881412997</c:v>
+                  <c:v>5.969931166005241</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5.847459736075888</c:v>
+                  <c:v>6.032401152286611</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.206430274061179</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -292,10 +298,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -337,16 +343,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$15</c:f>
+              <c:f>Sheet1!$C$2:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>21.14253081327848</c:v>
                 </c:pt>
@@ -378,16 +387,19 @@
                   <c:v>23.2658409452473</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>23.29035419471309</c:v>
+                  <c:v>23.29051230459681</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>23.70296034602906</c:v>
+                  <c:v>23.70393978024646</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>24.05824184969699</c:v>
+                  <c:v>24.12029341252871</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>24.41068033720871</c:v>
+                  <c:v>24.42619069491965</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>24.6638841025936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -417,10 +429,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -462,16 +474,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$15</c:f>
+              <c:f>Sheet1!$D$2:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>4.805619532540229</c:v>
                 </c:pt>
@@ -503,16 +518,19 @@
                   <c:v>5.829919788650906</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6.896192431372934</c:v>
+                  <c:v>6.896463207009411</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7.074830758206272</c:v>
+                  <c:v>7.073468706367995</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7.274859464489722</c:v>
+                  <c:v>7.320701339999563</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>7.532900020587258</c:v>
+                  <c:v>7.784432479425321</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8.239383087702379</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -542,10 +560,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -587,16 +605,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$15</c:f>
+              <c:f>Sheet1!$E$2:$E$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.2577562685535638</c:v>
                 </c:pt>
@@ -628,16 +649,19 @@
                   <c:v>0.2321867564071261</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.2273411952665313</c:v>
+                  <c:v>0.2277077096726701</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2227964407224829</c:v>
+                  <c:v>0.2231682146542828</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2147185885165654</c:v>
+                  <c:v>0.2145083894020202</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.2116792339428821</c:v>
+                  <c:v>0.2100973707580011</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.2010612672831956</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -667,10 +691,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -712,16 +736,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$15</c:f>
+              <c:f>Sheet1!$F$2:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2.499275435638963</c:v>
                 </c:pt>
@@ -753,16 +780,19 @@
                   <c:v>3.064910681652393</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.123279934704528</c:v>
+                  <c:v>3.123129018010502</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.210773783045608</c:v>
+                  <c:v>3.209797851028957</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.270637724800073</c:v>
+                  <c:v>3.258222758827947</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.330083110681771</c:v>
+                  <c:v>3.307782565279187</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.343795597296474</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -792,10 +822,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -837,16 +867,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$15</c:f>
+              <c:f>Sheet1!$G$2:$G$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>67.37599659754866</c:v>
                 </c:pt>
@@ -878,16 +911,19 @@
                   <c:v>61.80618851259435</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>60.66461246669349</c:v>
+                  <c:v>60.66273815500885</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>59.93558260320372</c:v>
+                  <c:v>59.93610756996297</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>59.31680449108365</c:v>
+                  <c:v>59.11634293323652</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>58.66719756150349</c:v>
+                  <c:v>58.23909573733124</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>57.34544567106317</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1006,13 +1042,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1428750</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1320,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" style="1" customWidth="1"/>
@@ -1590,22 +1626,22 @@
         <v>2020</v>
       </c>
       <c r="B12" s="2">
-        <v>5.798219777249421</v>
+        <v>5.799449605701753</v>
       </c>
       <c r="C12" s="2">
-        <v>23.29035419471309</v>
+        <v>23.29051230459681</v>
       </c>
       <c r="D12" s="2">
-        <v>6.896192431372934</v>
+        <v>6.896463207009411</v>
       </c>
       <c r="E12" s="2">
-        <v>0.2273411952665313</v>
+        <v>0.2277077096726701</v>
       </c>
       <c r="F12" s="2">
-        <v>3.123279934704528</v>
+        <v>3.123129018010502</v>
       </c>
       <c r="G12" s="2">
-        <v>60.66461246669349</v>
+        <v>60.66273815500885</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1613,22 +1649,22 @@
         <v>2021</v>
       </c>
       <c r="B13" s="2">
-        <v>5.853056068792861</v>
+        <v>5.853517877739331</v>
       </c>
       <c r="C13" s="2">
-        <v>23.70296034602906</v>
+        <v>23.70393978024646</v>
       </c>
       <c r="D13" s="2">
-        <v>7.074830758206272</v>
+        <v>7.073468706367995</v>
       </c>
       <c r="E13" s="2">
-        <v>0.2227964407224829</v>
+        <v>0.2231682146542828</v>
       </c>
       <c r="F13" s="2">
-        <v>3.210773783045608</v>
+        <v>3.209797851028957</v>
       </c>
       <c r="G13" s="2">
-        <v>59.93558260320372</v>
+        <v>59.93610756996297</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1636,22 +1672,22 @@
         <v>2022</v>
       </c>
       <c r="B14" s="2">
-        <v>5.864737881412997</v>
+        <v>5.969931166005241</v>
       </c>
       <c r="C14" s="2">
-        <v>24.05824184969699</v>
+        <v>24.12029341252871</v>
       </c>
       <c r="D14" s="2">
-        <v>7.274859464489722</v>
+        <v>7.320701339999563</v>
       </c>
       <c r="E14" s="2">
-        <v>0.2147185885165654</v>
+        <v>0.2145083894020202</v>
       </c>
       <c r="F14" s="2">
-        <v>3.270637724800073</v>
+        <v>3.258222758827947</v>
       </c>
       <c r="G14" s="2">
-        <v>59.31680449108365</v>
+        <v>59.11634293323652</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1659,22 +1695,45 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2">
-        <v>5.847459736075888</v>
+        <v>6.032401152286611</v>
       </c>
       <c r="C15" s="2">
-        <v>24.41068033720871</v>
+        <v>24.42619069491965</v>
       </c>
       <c r="D15" s="2">
-        <v>7.532900020587258</v>
+        <v>7.784432479425321</v>
       </c>
       <c r="E15" s="2">
-        <v>0.2116792339428821</v>
+        <v>0.2100973707580011</v>
       </c>
       <c r="F15" s="2">
-        <v>3.330083110681771</v>
+        <v>3.307782565279187</v>
       </c>
       <c r="G15" s="2">
-        <v>58.66719756150349</v>
+        <v>58.23909573733124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="2">
+        <v>6.206430274061179</v>
+      </c>
+      <c r="C16" s="2">
+        <v>24.6638841025936</v>
+      </c>
+      <c r="D16" s="2">
+        <v>8.239383087702379</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.2010612672831956</v>
+      </c>
+      <c r="F16" s="2">
+        <v>3.343795597296474</v>
+      </c>
+      <c r="G16" s="2">
+        <v>57.34544567106317</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/0500000US39049.xlsx
+++ b/output_data/charts/0500000US39049.xlsx
@@ -226,34 +226,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>3.91882135244011</c:v>
+                  <c:v>3.917503142680256</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.062012825626187</c:v>
+                  <c:v>4.054708672086721</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.215026470556353</c:v>
+                  <c:v>4.20234436572439</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.440421724002737</c:v>
+                  <c:v>4.421771498049845</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.702855602143438</c:v>
+                  <c:v>4.676984597395592</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.00122824632659</c:v>
+                  <c:v>4.968164111895631</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.268143649840183</c:v>
+                  <c:v>5.214877005767193</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.512992392627436</c:v>
+                  <c:v>5.443184537363663</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.65727163172217</c:v>
+                  <c:v>5.5742227945596</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.800953315447926</c:v>
+                  <c:v>5.675463031875306</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>5.799449605701753</c:v>
@@ -357,34 +357,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>21.14253081327848</c:v>
+                  <c:v>21.14342112258425</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21.32122748677511</c:v>
+                  <c:v>21.3242716802168</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>21.50990154737475</c:v>
+                  <c:v>21.51528925102894</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>21.70817250198083</c:v>
+                  <c:v>21.71734989063713</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>21.96345048831168</c:v>
+                  <c:v>21.97588427293473</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>22.22680661519957</c:v>
+                  <c:v>22.24424321568715</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>22.47367496541752</c:v>
+                  <c:v>22.49166307034407</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>22.71628403531697</c:v>
+                  <c:v>22.71561006862163</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>23.04242934619391</c:v>
+                  <c:v>22.98887051903421</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>23.2658409452473</c:v>
+                  <c:v>23.16123868051484</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>23.29051230459681</c:v>
@@ -488,34 +488,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>4.805619532540229</c:v>
+                  <c:v>4.806114206629726</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.861391613466484</c:v>
+                  <c:v>4.862212059620596</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.930302679075461</c:v>
+                  <c:v>4.933426185005567</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.024089843551353</c:v>
+                  <c:v>5.028887222511194</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.115365551625096</c:v>
+                  <c:v>5.122653957405024</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.234475801162422</c:v>
+                  <c:v>5.244451584477638</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.368832790155676</c:v>
+                  <c:v>5.37996782925968</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.531119877442775</c:v>
+                  <c:v>5.537664703475851</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.67599394466907</c:v>
+                  <c:v>5.665604749720502</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.829919788650906</c:v>
+                  <c:v>5.781101434130545</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>6.896463207009411</c:v>
@@ -619,34 +619,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.2577562685535638</c:v>
+                  <c:v>0.2578455533432459</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.2519228701085682</c:v>
+                  <c:v>0.2525406504065041</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2516558168932931</c:v>
+                  <c:v>0.2514501123811033</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.251069155977841</c:v>
+                  <c:v>0.2497378736838305</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2452456411986845</c:v>
+                  <c:v>0.2431437657163253</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.244377295012048</c:v>
+                  <c:v>0.2420100112455523</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2421558140920882</c:v>
+                  <c:v>0.2390835262269999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.2371229290312827</c:v>
+                  <c:v>0.2341934836473667</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.235366219903882</c:v>
+                  <c:v>0.2317048737552554</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2321867564071261</c:v>
+                  <c:v>0.2269213126805574</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.2277077096726701</c:v>
@@ -750,34 +750,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>2.499275435638963</c:v>
+                  <c:v>2.497251762559145</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.568766475544005</c:v>
+                  <c:v>2.560721544715447</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.614118575084406</c:v>
+                  <c:v>2.600319420872444</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.690893760262995</c:v>
+                  <c:v>2.672621870277419</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.743554431131827</c:v>
+                  <c:v>2.719721696886694</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.811054375935594</c:v>
+                  <c:v>2.781007582397132</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.880226974024711</c:v>
+                  <c:v>2.846561261720742</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.938735272382816</c:v>
+                  <c:v>2.899398692406851</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.997633346808304</c:v>
+                  <c:v>2.951369505803327</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.064910681652393</c:v>
+                  <c:v>3.016504196677289</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>3.123129018010502</c:v>
@@ -881,34 +881,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>67.37599659754866</c:v>
+                  <c:v>67.37786421220338</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>66.93467872847964</c:v>
+                  <c:v>66.94554539295393</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>66.47899491101573</c:v>
+                  <c:v>66.49717066498755</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>65.88535301422425</c:v>
+                  <c:v>65.90963164484059</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>65.22952828558928</c:v>
+                  <c:v>65.26161170966164</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>64.48205766636377</c:v>
+                  <c:v>64.5201234942969</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>63.76696580646982</c:v>
+                  <c:v>63.82784730668132</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>63.06374549319872</c:v>
+                  <c:v>63.16994851448464</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>62.39130551070267</c:v>
+                  <c:v>62.58822755712711</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>61.80618851259435</c:v>
+                  <c:v>62.13877134412146</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>60.66273815500885</c:v>
@@ -1396,22 +1396,22 @@
         <v>2010</v>
       </c>
       <c r="B2" s="2">
-        <v>3.91882135244011</v>
+        <v>3.917503142680256</v>
       </c>
       <c r="C2" s="2">
-        <v>21.14253081327848</v>
+        <v>21.14342112258425</v>
       </c>
       <c r="D2" s="2">
-        <v>4.805619532540229</v>
+        <v>4.806114206629726</v>
       </c>
       <c r="E2" s="2">
-        <v>0.2577562685535638</v>
+        <v>0.2578455533432459</v>
       </c>
       <c r="F2" s="2">
-        <v>2.499275435638963</v>
+        <v>2.497251762559145</v>
       </c>
       <c r="G2" s="2">
-        <v>67.37599659754866</v>
+        <v>67.37786421220338</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1419,22 +1419,22 @@
         <v>2011</v>
       </c>
       <c r="B3" s="2">
-        <v>4.062012825626187</v>
+        <v>4.054708672086721</v>
       </c>
       <c r="C3" s="2">
-        <v>21.32122748677511</v>
+        <v>21.3242716802168</v>
       </c>
       <c r="D3" s="2">
-        <v>4.861391613466484</v>
+        <v>4.862212059620596</v>
       </c>
       <c r="E3" s="2">
-        <v>0.2519228701085682</v>
+        <v>0.2525406504065041</v>
       </c>
       <c r="F3" s="2">
-        <v>2.568766475544005</v>
+        <v>2.560721544715447</v>
       </c>
       <c r="G3" s="2">
-        <v>66.93467872847964</v>
+        <v>66.94554539295393</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1442,22 +1442,22 @@
         <v>2012</v>
       </c>
       <c r="B4" s="2">
-        <v>4.215026470556353</v>
+        <v>4.20234436572439</v>
       </c>
       <c r="C4" s="2">
-        <v>21.50990154737475</v>
+        <v>21.51528925102894</v>
       </c>
       <c r="D4" s="2">
-        <v>4.930302679075461</v>
+        <v>4.933426185005567</v>
       </c>
       <c r="E4" s="2">
-        <v>0.2516558168932931</v>
+        <v>0.2514501123811033</v>
       </c>
       <c r="F4" s="2">
-        <v>2.614118575084406</v>
+        <v>2.600319420872444</v>
       </c>
       <c r="G4" s="2">
-        <v>66.47899491101573</v>
+        <v>66.49717066498755</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1465,22 +1465,22 @@
         <v>2013</v>
       </c>
       <c r="B5" s="2">
-        <v>4.440421724002737</v>
+        <v>4.421771498049845</v>
       </c>
       <c r="C5" s="2">
-        <v>21.70817250198083</v>
+        <v>21.71734989063713</v>
       </c>
       <c r="D5" s="2">
-        <v>5.024089843551353</v>
+        <v>5.028887222511194</v>
       </c>
       <c r="E5" s="2">
-        <v>0.251069155977841</v>
+        <v>0.2497378736838305</v>
       </c>
       <c r="F5" s="2">
-        <v>2.690893760262995</v>
+        <v>2.672621870277419</v>
       </c>
       <c r="G5" s="2">
-        <v>65.88535301422425</v>
+        <v>65.90963164484059</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1488,22 +1488,22 @@
         <v>2014</v>
       </c>
       <c r="B6" s="2">
-        <v>4.702855602143438</v>
+        <v>4.676984597395592</v>
       </c>
       <c r="C6" s="2">
-        <v>21.96345048831168</v>
+        <v>21.97588427293473</v>
       </c>
       <c r="D6" s="2">
-        <v>5.115365551625096</v>
+        <v>5.122653957405024</v>
       </c>
       <c r="E6" s="2">
-        <v>0.2452456411986845</v>
+        <v>0.2431437657163253</v>
       </c>
       <c r="F6" s="2">
-        <v>2.743554431131827</v>
+        <v>2.719721696886694</v>
       </c>
       <c r="G6" s="2">
-        <v>65.22952828558928</v>
+        <v>65.26161170966164</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1511,22 +1511,22 @@
         <v>2015</v>
       </c>
       <c r="B7" s="2">
-        <v>5.00122824632659</v>
+        <v>4.968164111895631</v>
       </c>
       <c r="C7" s="2">
-        <v>22.22680661519957</v>
+        <v>22.24424321568715</v>
       </c>
       <c r="D7" s="2">
-        <v>5.234475801162422</v>
+        <v>5.244451584477638</v>
       </c>
       <c r="E7" s="2">
-        <v>0.244377295012048</v>
+        <v>0.2420100112455523</v>
       </c>
       <c r="F7" s="2">
-        <v>2.811054375935594</v>
+        <v>2.781007582397132</v>
       </c>
       <c r="G7" s="2">
-        <v>64.48205766636377</v>
+        <v>64.5201234942969</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1534,22 +1534,22 @@
         <v>2016</v>
       </c>
       <c r="B8" s="2">
-        <v>5.268143649840183</v>
+        <v>5.214877005767193</v>
       </c>
       <c r="C8" s="2">
-        <v>22.47367496541752</v>
+        <v>22.49166307034407</v>
       </c>
       <c r="D8" s="2">
-        <v>5.368832790155676</v>
+        <v>5.37996782925968</v>
       </c>
       <c r="E8" s="2">
-        <v>0.2421558140920882</v>
+        <v>0.2390835262269999</v>
       </c>
       <c r="F8" s="2">
-        <v>2.880226974024711</v>
+        <v>2.846561261720742</v>
       </c>
       <c r="G8" s="2">
-        <v>63.76696580646982</v>
+        <v>63.82784730668132</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1557,22 +1557,22 @@
         <v>2017</v>
       </c>
       <c r="B9" s="2">
-        <v>5.512992392627436</v>
+        <v>5.443184537363663</v>
       </c>
       <c r="C9" s="2">
-        <v>22.71628403531697</v>
+        <v>22.71561006862163</v>
       </c>
       <c r="D9" s="2">
-        <v>5.531119877442775</v>
+        <v>5.537664703475851</v>
       </c>
       <c r="E9" s="2">
-        <v>0.2371229290312827</v>
+        <v>0.2341934836473667</v>
       </c>
       <c r="F9" s="2">
-        <v>2.938735272382816</v>
+        <v>2.899398692406851</v>
       </c>
       <c r="G9" s="2">
-        <v>63.06374549319872</v>
+        <v>63.16994851448464</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1580,22 +1580,22 @@
         <v>2018</v>
       </c>
       <c r="B10" s="2">
-        <v>5.65727163172217</v>
+        <v>5.5742227945596</v>
       </c>
       <c r="C10" s="2">
-        <v>23.04242934619391</v>
+        <v>22.98887051903421</v>
       </c>
       <c r="D10" s="2">
-        <v>5.67599394466907</v>
+        <v>5.665604749720502</v>
       </c>
       <c r="E10" s="2">
-        <v>0.235366219903882</v>
+        <v>0.2317048737552554</v>
       </c>
       <c r="F10" s="2">
-        <v>2.997633346808304</v>
+        <v>2.951369505803327</v>
       </c>
       <c r="G10" s="2">
-        <v>62.39130551070267</v>
+        <v>62.58822755712711</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1603,22 +1603,22 @@
         <v>2019</v>
       </c>
       <c r="B11" s="2">
-        <v>5.800953315447926</v>
+        <v>5.675463031875306</v>
       </c>
       <c r="C11" s="2">
-        <v>23.2658409452473</v>
+        <v>23.16123868051484</v>
       </c>
       <c r="D11" s="2">
-        <v>5.829919788650906</v>
+        <v>5.781101434130545</v>
       </c>
       <c r="E11" s="2">
-        <v>0.2321867564071261</v>
+        <v>0.2269213126805574</v>
       </c>
       <c r="F11" s="2">
-        <v>3.064910681652393</v>
+        <v>3.016504196677289</v>
       </c>
       <c r="G11" s="2">
-        <v>61.80618851259435</v>
+        <v>62.13877134412146</v>
       </c>
     </row>
     <row r="12" spans="1:7">
